--- a/Team-Data/2012-13/1-20-2012-13.xlsx
+++ b/Team-Data/2012-13/1-20-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -751,10 +818,10 @@
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ2" t="n">
         <v>22</v>
@@ -769,7 +836,7 @@
         <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="n">
         <v>28</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -843,91 +910,91 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5</v>
+        <v>0.513</v>
       </c>
       <c r="H3" t="n">
         <v>48.9</v>
       </c>
       <c r="I3" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J3" t="n">
-        <v>79.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="K3" t="n">
-        <v>0.461</v>
+        <v>0.463</v>
       </c>
       <c r="L3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M3" t="n">
         <v>16.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.337</v>
+        <v>0.339</v>
       </c>
       <c r="O3" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P3" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.773</v>
+        <v>0.775</v>
       </c>
       <c r="R3" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="S3" t="n">
         <v>30.4</v>
       </c>
       <c r="T3" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="U3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V3" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W3" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
         <v>4.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
         <v>16</v>
       </c>
       <c r="AF3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="n">
         <v>15</v>
@@ -936,7 +1003,7 @@
         <v>4</v>
       </c>
       <c r="AI3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ3" t="n">
         <v>27</v>
@@ -951,7 +1018,7 @@
         <v>28</v>
       </c>
       <c r="AN3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
         <v>24</v>
@@ -969,7 +1036,7 @@
         <v>18</v>
       </c>
       <c r="AT3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AU3" t="n">
         <v>6</v>
@@ -984,19 +1051,19 @@
         <v>26</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BA3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BB3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BC3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -1103,10 +1170,10 @@
         <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF4" t="n">
         <v>8</v>
@@ -1115,7 +1182,7 @@
         <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
         <v>26</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>28</v>
@@ -1297,13 +1364,13 @@
         <v>28</v>
       </c>
       <c r="AH5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI5" t="n">
         <v>28</v>
       </c>
       <c r="AJ5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
@@ -1342,7 +1409,7 @@
         <v>6</v>
       </c>
       <c r="AW5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX5" t="n">
         <v>5</v>
@@ -1351,13 +1418,13 @@
         <v>30</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>2.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE6" t="n">
         <v>11</v>
@@ -1479,7 +1546,7 @@
         <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI6" t="n">
         <v>25</v>
@@ -1497,7 +1564,7 @@
         <v>30</v>
       </c>
       <c r="AN6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO6" t="n">
         <v>8</v>
@@ -1536,7 +1603,7 @@
         <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
         <v>25</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-5.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
@@ -1706,7 +1773,7 @@
         <v>15</v>
       </c>
       <c r="AW7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX7" t="n">
         <v>30</v>
@@ -1721,7 +1788,7 @@
         <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -1753,46 +1820,46 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8" t="n">
         <v>24</v>
       </c>
       <c r="G8" t="n">
-        <v>0.429</v>
+        <v>0.415</v>
       </c>
       <c r="H8" t="n">
         <v>49.2</v>
       </c>
       <c r="I8" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J8" t="n">
-        <v>84</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L8" t="n">
         <v>7</v>
       </c>
       <c r="M8" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.359</v>
+        <v>0.356</v>
       </c>
       <c r="O8" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.794</v>
+        <v>0.793</v>
       </c>
       <c r="R8" t="n">
         <v>9.4</v>
@@ -1804,10 +1871,10 @@
         <v>41.9</v>
       </c>
       <c r="U8" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="V8" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="W8" t="n">
         <v>7.8</v>
@@ -1819,19 +1886,19 @@
         <v>4.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>100.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>-2.8</v>
+        <v>-3</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>18</v>
@@ -1840,13 +1907,13 @@
         <v>21</v>
       </c>
       <c r="AG8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH8" t="n">
         <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ8" t="n">
         <v>5</v>
@@ -1861,16 +1928,16 @@
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AO8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AP8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR8" t="n">
         <v>27</v>
@@ -1882,10 +1949,10 @@
         <v>18</v>
       </c>
       <c r="AU8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV8" t="n">
         <v>13</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>11</v>
       </c>
       <c r="AW8" t="n">
         <v>15</v>
@@ -1897,10 +1964,10 @@
         <v>8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BB8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -1935,61 +2002,61 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>0.581</v>
+        <v>0.571</v>
       </c>
       <c r="H9" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="J9" t="n">
-        <v>85.2</v>
+        <v>85</v>
       </c>
       <c r="K9" t="n">
         <v>0.465</v>
       </c>
       <c r="L9" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M9" t="n">
         <v>18.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0.331</v>
+        <v>0.328</v>
       </c>
       <c r="O9" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>25.8</v>
       </c>
       <c r="Q9" t="n">
         <v>0.681</v>
       </c>
       <c r="R9" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="S9" t="n">
         <v>31.7</v>
       </c>
       <c r="T9" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
       <c r="U9" t="n">
         <v>23.5</v>
       </c>
       <c r="V9" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="W9" t="n">
         <v>8.199999999999999</v>
@@ -1998,25 +2065,25 @@
         <v>6.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.1</v>
+        <v>102.7</v>
       </c>
       <c r="AC9" t="n">
         <v>2.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF9" t="n">
         <v>11</v>
@@ -2025,7 +2092,7 @@
         <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
         <v>2</v>
@@ -2046,10 +2113,10 @@
         <v>29</v>
       </c>
       <c r="AO9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ9" t="n">
         <v>30</v>
@@ -2064,13 +2131,13 @@
         <v>2</v>
       </c>
       <c r="AU9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AW9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
@@ -2079,13 +2146,13 @@
         <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC9" t="n">
         <v>7</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F10" t="n">
         <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>0.375</v>
+        <v>0.359</v>
       </c>
       <c r="H10" t="n">
         <v>48.6</v>
@@ -2135,25 +2202,25 @@
         <v>35.9</v>
       </c>
       <c r="J10" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L10" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M10" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.376</v>
+        <v>0.373</v>
       </c>
       <c r="O10" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P10" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="Q10" t="n">
         <v>0.709</v>
@@ -2162,40 +2229,40 @@
         <v>12.5</v>
       </c>
       <c r="S10" t="n">
-        <v>31.1</v>
+        <v>30.9</v>
       </c>
       <c r="T10" t="n">
-        <v>43.6</v>
+        <v>43.4</v>
       </c>
       <c r="U10" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V10" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="W10" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X10" t="n">
         <v>5.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>21.1</v>
+        <v>20.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.1</v>
+        <v>-1.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2225,7 +2292,7 @@
         <v>26</v>
       </c>
       <c r="AN10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO10" t="n">
         <v>17</v>
@@ -2264,10 +2331,10 @@
         <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC10" t="n">
         <v>18</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>1.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF11" t="n">
         <v>7</v>
@@ -2389,16 +2456,16 @@
         <v>7</v>
       </c>
       <c r="AH11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ11" t="n">
         <v>12</v>
       </c>
       <c r="AK11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
@@ -2407,7 +2474,7 @@
         <v>12</v>
       </c>
       <c r="AN11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO11" t="n">
         <v>16</v>
@@ -2431,7 +2498,7 @@
         <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW11" t="n">
         <v>26</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>1.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>14</v>
@@ -2568,13 +2635,13 @@
         <v>18</v>
       </c>
       <c r="AG12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ12" t="n">
         <v>10</v>
@@ -2589,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
         <v>5</v>
@@ -2610,7 +2677,7 @@
         <v>12</v>
       </c>
       <c r="AU12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
@@ -2625,7 +2692,7 @@
         <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
         <v>17</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>2.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
         <v>6</v>
@@ -2753,7 +2820,7 @@
         <v>8</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>30</v>
@@ -2777,7 +2844,7 @@
         <v>20</v>
       </c>
       <c r="AP13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ13" t="n">
         <v>23</v>
@@ -2810,7 +2877,7 @@
         <v>11</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -2923,16 +2990,16 @@
         <v>8.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="n">
         <v>30</v>
@@ -2956,7 +3023,7 @@
         <v>17</v>
       </c>
       <c r="AO14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP14" t="n">
         <v>8</v>
@@ -2974,7 +3041,7 @@
         <v>16</v>
       </c>
       <c r="AU14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV14" t="n">
         <v>9</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -3027,55 +3094,55 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E15" t="n">
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G15" t="n">
-        <v>0.425</v>
+        <v>0.436</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K15" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L15" t="n">
         <v>9</v>
       </c>
       <c r="M15" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O15" t="n">
         <v>19.6</v>
       </c>
       <c r="P15" t="n">
-        <v>28.2</v>
+        <v>28.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.694</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="R15" t="n">
         <v>12.4</v>
       </c>
       <c r="S15" t="n">
-        <v>32.7</v>
+        <v>32.9</v>
       </c>
       <c r="T15" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="U15" t="n">
         <v>22.1</v>
@@ -3093,7 +3160,7 @@
         <v>4.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA15" t="n">
         <v>23.2</v>
@@ -3102,19 +3169,19 @@
         <v>103.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF15" t="n">
         <v>19</v>
       </c>
       <c r="AG15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH15" t="n">
         <v>29</v>
@@ -3123,7 +3190,7 @@
         <v>11</v>
       </c>
       <c r="AJ15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK15" t="n">
         <v>9</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO15" t="n">
         <v>3</v>
@@ -3156,10 +3223,10 @@
         <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV15" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AW15" t="n">
         <v>20</v>
@@ -3168,16 +3235,16 @@
         <v>10</v>
       </c>
       <c r="AY15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
       </c>
       <c r="BB15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC15" t="n">
         <v>11</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3299,7 +3366,7 @@
         <v>5</v>
       </c>
       <c r="AH16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI16" t="n">
         <v>23</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3548,7 @@
         <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI17" t="n">
         <v>4</v>
@@ -3502,7 +3569,7 @@
         <v>3</v>
       </c>
       <c r="AO17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
@@ -3517,7 +3584,7 @@
         <v>15</v>
       </c>
       <c r="AT17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AU17" t="n">
         <v>12</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-0.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE18" t="n">
         <v>14</v>
@@ -3666,7 +3733,7 @@
         <v>25</v>
       </c>
       <c r="AI18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
@@ -3681,7 +3748,7 @@
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO18" t="n">
         <v>22</v>
@@ -3717,7 +3784,7 @@
         <v>5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA18" t="n">
         <v>16</v>
@@ -3726,7 +3793,7 @@
         <v>15</v>
       </c>
       <c r="BC18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -3836,10 +3903,10 @@
         <v>30</v>
       </c>
       <c r="AE19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG19" t="n">
         <v>18</v>
@@ -3869,7 +3936,7 @@
         <v>4</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ19" t="n">
         <v>22</v>
@@ -3887,7 +3954,7 @@
         <v>19</v>
       </c>
       <c r="AV19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW19" t="n">
         <v>17</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-4</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE20" t="n">
         <v>26</v>
@@ -4027,7 +4094,7 @@
         <v>26</v>
       </c>
       <c r="AH20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI20" t="n">
         <v>22</v>
@@ -4054,7 +4121,7 @@
         <v>28</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
         <v>17</v>
@@ -4069,7 +4136,7 @@
         <v>21</v>
       </c>
       <c r="AV20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW20" t="n">
         <v>28</v>
@@ -4081,7 +4148,7 @@
         <v>26</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4330,7 @@
         <v>2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -4301,19 +4368,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E22" t="n">
         <v>32</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="H22" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I22" t="n">
         <v>37.7</v>
@@ -4328,16 +4395,16 @@
         <v>7.6</v>
       </c>
       <c r="M22" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.388</v>
+        <v>0.389</v>
       </c>
       <c r="O22" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="P22" t="n">
-        <v>27.6</v>
+        <v>27.1</v>
       </c>
       <c r="Q22" t="n">
         <v>0.838</v>
@@ -4346,40 +4413,40 @@
         <v>10.7</v>
       </c>
       <c r="S22" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T22" t="n">
-        <v>43.2</v>
+        <v>43.4</v>
       </c>
       <c r="U22" t="n">
         <v>21.6</v>
       </c>
       <c r="V22" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="W22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="Y22" t="n">
         <v>4.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>106</v>
+        <v>105.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4391,10 +4458,10 @@
         <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AI22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ22" t="n">
         <v>29</v>
@@ -4409,7 +4476,7 @@
         <v>15</v>
       </c>
       <c r="AN22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4436,7 +4503,7 @@
         <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4448,7 +4515,7 @@
         <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BB22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -4483,58 +4550,58 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E23" t="n">
         <v>14</v>
       </c>
       <c r="F23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>0.35</v>
+        <v>0.359</v>
       </c>
       <c r="H23" t="n">
         <v>48.4</v>
       </c>
       <c r="I23" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J23" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L23" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M23" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.355</v>
+        <v>0.353</v>
       </c>
       <c r="O23" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="P23" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="Q23" t="n">
         <v>0.784</v>
       </c>
       <c r="R23" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S23" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T23" t="n">
         <v>42.5</v>
       </c>
       <c r="U23" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V23" t="n">
         <v>14.7</v>
@@ -4543,46 +4610,46 @@
         <v>5.9</v>
       </c>
       <c r="X23" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-3.4</v>
+        <v>-3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AE23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AH23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ23" t="n">
         <v>13</v>
       </c>
       <c r="AK23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL23" t="n">
         <v>16</v>
@@ -4591,7 +4658,7 @@
         <v>17</v>
       </c>
       <c r="AN23" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4624,16 +4691,16 @@
         <v>25</v>
       </c>
       <c r="AY23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>14</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>12</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC23" t="n">
         <v>23</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -4743,13 +4810,13 @@
         <v>-4.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG24" t="n">
         <v>20</v>
@@ -4773,7 +4840,7 @@
         <v>22</v>
       </c>
       <c r="AN24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-4.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>26</v>
@@ -4937,7 +5004,7 @@
         <v>27</v>
       </c>
       <c r="AH25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI25" t="n">
         <v>10</v>
@@ -4982,7 +5049,7 @@
         <v>5</v>
       </c>
       <c r="AW25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX25" t="n">
         <v>8</v>
@@ -4991,7 +5058,7 @@
         <v>18</v>
       </c>
       <c r="AZ25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA25" t="n">
         <v>28</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -5107,22 +5174,22 @@
         <v>-2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
         <v>16</v>
       </c>
       <c r="AF26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ26" t="n">
         <v>9</v>
@@ -5137,7 +5204,7 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO26" t="n">
         <v>18</v>
@@ -5146,7 +5213,7 @@
         <v>20</v>
       </c>
       <c r="AQ26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR26" t="n">
         <v>13</v>
@@ -5173,7 +5240,7 @@
         <v>4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA26" t="n">
         <v>24</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-5.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>22</v>
@@ -5301,7 +5368,7 @@
         <v>22</v>
       </c>
       <c r="AH27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI27" t="n">
         <v>18</v>
@@ -5310,7 +5377,7 @@
         <v>8</v>
       </c>
       <c r="AK27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL27" t="n">
         <v>17</v>
@@ -5319,7 +5386,7 @@
         <v>18</v>
       </c>
       <c r="AN27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO27" t="n">
         <v>15</v>
@@ -5343,7 +5410,7 @@
         <v>27</v>
       </c>
       <c r="AV27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW27" t="n">
         <v>14</v>
@@ -5358,7 +5425,7 @@
         <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB27" t="n">
         <v>14</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -5483,13 +5550,13 @@
         <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5510,7 +5577,7 @@
         <v>24</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR28" t="n">
         <v>29</v>
@@ -5534,7 +5601,7 @@
         <v>11</v>
       </c>
       <c r="AY28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F29" t="n">
         <v>26</v>
       </c>
       <c r="G29" t="n">
-        <v>0.366</v>
+        <v>0.35</v>
       </c>
       <c r="H29" t="n">
         <v>49</v>
       </c>
       <c r="I29" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="J29" t="n">
         <v>82.2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.442</v>
+        <v>0.439</v>
       </c>
       <c r="L29" t="n">
         <v>7.6</v>
@@ -5605,19 +5672,19 @@
         <v>21.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O29" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="P29" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.771</v>
+        <v>0.775</v>
       </c>
       <c r="R29" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S29" t="n">
         <v>29.3</v>
@@ -5626,13 +5693,13 @@
         <v>40.1</v>
       </c>
       <c r="U29" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V29" t="n">
         <v>12.9</v>
       </c>
       <c r="W29" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X29" t="n">
         <v>4.6</v>
@@ -5644,25 +5711,25 @@
         <v>22.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.9</v>
+        <v>-2.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
       </c>
       <c r="AF29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH29" t="n">
         <v>2</v>
@@ -5674,7 +5741,7 @@
         <v>15</v>
       </c>
       <c r="AK29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
@@ -5686,13 +5753,13 @@
         <v>19</v>
       </c>
       <c r="AO29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP29" t="n">
         <v>13</v>
       </c>
       <c r="AQ29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AR29" t="n">
         <v>21</v>
@@ -5704,13 +5771,13 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV29" t="n">
         <v>3</v>
       </c>
       <c r="AW29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX29" t="n">
         <v>24</v>
@@ -5722,7 +5789,7 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BB29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>0.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
         <v>12</v>
@@ -5847,7 +5914,7 @@
         <v>14</v>
       </c>
       <c r="AH30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI30" t="n">
         <v>17</v>
@@ -5904,7 +5971,7 @@
         <v>29</v>
       </c>
       <c r="BA30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BB30" t="n">
         <v>11</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-20-2012-13</t>
+          <t>2013-01-20</t>
         </is>
       </c>
     </row>
